--- a/VerveStacks_NGA/vt_vervestacks_NGA_v1.xlsx
+++ b/VerveStacks_NGA/vt_vervestacks_NGA_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF98CDC3-C971-4A7D-A9F9-D865789472C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B31A3094-5953-45E4-9F21-B2FBCBE7DEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2E242213-4140-45FA-99C4-3776DCEBBA9E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A99EEE5C-0695-459D-9EE7-2925C3B1DF79}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2482,7 +2482,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{479F5DD7-49C1-46FF-BF70-9800A69A9E8D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE579F9B-4C0D-4587-A2CC-D84AF244A979}">
   <dimension ref="B9:T111"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8212,7 +8212,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0248EB9D-3F62-49A5-8C49-7488B88C588B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ED10B42-E88B-48DF-BCEF-7533198D3F95}">
   <dimension ref="B9:T118"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14049,7 +14049,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E00B3A35-2256-4647-8E6B-B36EFE9E1BD4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84A627A1-2066-4568-BDBF-F241FE99539F}">
   <dimension ref="B9:T129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19855,7 +19855,7 @@
         <v>33</v>
       </c>
       <c r="L119">
-        <v>0.21312123749313963</v>
+        <v>0.2131212374931396</v>
       </c>
       <c r="N119" t="s">
         <v>154</v>
@@ -19902,7 +19902,7 @@
         <v>33</v>
       </c>
       <c r="L120">
-        <v>0.21312123749313963</v>
+        <v>0.2131212374931396</v>
       </c>
       <c r="N120" t="s">
         <v>154</v>
@@ -19949,7 +19949,7 @@
         <v>33</v>
       </c>
       <c r="L121">
-        <v>0.21312123749313963</v>
+        <v>0.2131212374931396</v>
       </c>
       <c r="N121" t="s">
         <v>154</v>
@@ -20406,7 +20406,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{518DBB6C-63F9-4B9C-ADD0-157169D858CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9840C105-7F56-4F90-8AE1-2253BA0D5B9C}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
